--- a/output/DTR_8-5_Jennettee_F._Haro.xlsx
+++ b/output/DTR_8-5_Jennettee_F._Haro.xlsx
@@ -1125,12 +1125,16 @@
       <c r="J20" s="24"/>
     </row>
     <row r="21" spans="1:10">
-      <c r="A21" s="21"/>
+      <c r="A21" s="21">
+        <v>3</v>
+      </c>
       <c r="B21" s="22"/>
       <c r="C21" s="22"/>
       <c r="D21" s="22"/>
       <c r="E21" s="23"/>
-      <c r="F21" s="21"/>
+      <c r="F21" s="21" t="s">
+        <v>19</v>
+      </c>
       <c r="G21" s="21"/>
       <c r="H21" s="25" t="s">
         <v>19</v>
@@ -1139,12 +1143,16 @@
       <c r="J21" s="25"/>
     </row>
     <row r="22" spans="1:10">
-      <c r="A22" s="21"/>
+      <c r="A22" s="21">
+        <v>4</v>
+      </c>
       <c r="B22" s="22"/>
       <c r="C22" s="22"/>
       <c r="D22" s="22"/>
       <c r="E22" s="22"/>
-      <c r="F22" s="21"/>
+      <c r="F22" s="21" t="s">
+        <v>20</v>
+      </c>
       <c r="G22" s="21"/>
       <c r="H22" s="25" t="s">
         <v>20</v>
@@ -1243,12 +1251,16 @@
       <c r="J27" s="27"/>
     </row>
     <row r="28" spans="1:10">
-      <c r="A28" s="21"/>
+      <c r="A28" s="21">
+        <v>10</v>
+      </c>
       <c r="B28" s="22"/>
       <c r="C28" s="22"/>
       <c r="D28" s="22"/>
       <c r="E28" s="22"/>
-      <c r="F28" s="21"/>
+      <c r="F28" s="21" t="s">
+        <v>19</v>
+      </c>
       <c r="G28" s="21"/>
       <c r="H28" s="25" t="s">
         <v>19</v>
@@ -1257,12 +1269,16 @@
       <c r="J28" s="25"/>
     </row>
     <row r="29" spans="1:10">
-      <c r="A29" s="21"/>
+      <c r="A29" s="21">
+        <v>11</v>
+      </c>
       <c r="B29" s="22"/>
       <c r="C29" s="22"/>
       <c r="D29" s="22"/>
       <c r="E29" s="22"/>
-      <c r="F29" s="21"/>
+      <c r="F29" s="21" t="s">
+        <v>20</v>
+      </c>
       <c r="G29" s="21"/>
       <c r="H29" s="25" t="s">
         <v>20</v>
@@ -1371,12 +1387,16 @@
       <c r="J34" s="25"/>
     </row>
     <row r="35" spans="1:10">
-      <c r="A35" s="21"/>
+      <c r="A35" s="21">
+        <v>17</v>
+      </c>
       <c r="B35" s="22"/>
       <c r="C35" s="22"/>
       <c r="D35" s="22"/>
       <c r="E35" s="22"/>
-      <c r="F35" s="21"/>
+      <c r="F35" s="21" t="s">
+        <v>19</v>
+      </c>
       <c r="G35" s="21"/>
       <c r="H35" s="25" t="s">
         <v>19</v>
@@ -1385,12 +1405,16 @@
       <c r="J35" s="25"/>
     </row>
     <row r="36" spans="1:10">
-      <c r="A36" s="21"/>
+      <c r="A36" s="21">
+        <v>18</v>
+      </c>
       <c r="B36" s="22"/>
       <c r="C36" s="22"/>
       <c r="D36" s="22"/>
       <c r="E36" s="22"/>
-      <c r="F36" s="21"/>
+      <c r="F36" s="21" t="s">
+        <v>20</v>
+      </c>
       <c r="G36" s="21"/>
       <c r="H36" s="25" t="s">
         <v>20</v>
@@ -1475,12 +1499,16 @@
       <c r="J41" s="25"/>
     </row>
     <row r="42" spans="1:10">
-      <c r="A42" s="21"/>
+      <c r="A42" s="21">
+        <v>24</v>
+      </c>
       <c r="B42" s="22"/>
       <c r="C42" s="23"/>
       <c r="D42" s="23"/>
       <c r="E42" s="22"/>
-      <c r="F42" s="21"/>
+      <c r="F42" s="21" t="s">
+        <v>19</v>
+      </c>
       <c r="G42" s="21"/>
       <c r="H42" s="25" t="s">
         <v>19</v>
@@ -1489,12 +1517,16 @@
       <c r="J42" s="25"/>
     </row>
     <row r="43" spans="1:10">
-      <c r="A43" s="21"/>
+      <c r="A43" s="21">
+        <v>25</v>
+      </c>
       <c r="B43" s="22"/>
       <c r="C43" s="22"/>
       <c r="D43" s="22"/>
       <c r="E43" s="22"/>
-      <c r="F43" s="21"/>
+      <c r="F43" s="21" t="s">
+        <v>20</v>
+      </c>
       <c r="G43" s="21"/>
       <c r="H43" s="25" t="s">
         <v>20</v>
@@ -1577,12 +1609,16 @@
       <c r="J48" s="25"/>
     </row>
     <row r="49" spans="1:10">
-      <c r="A49" s="21"/>
+      <c r="A49" s="21">
+        <v>31</v>
+      </c>
       <c r="B49" s="23"/>
       <c r="C49" s="23"/>
       <c r="D49" s="23"/>
       <c r="E49" s="23"/>
-      <c r="F49" s="21"/>
+      <c r="F49" s="21" t="s">
+        <v>19</v>
+      </c>
       <c r="G49" s="21"/>
       <c r="H49" s="25" t="s">
         <v>19</v>
